--- a/exports/SIEMENS_full_report.xlsx
+++ b/exports/SIEMENS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.16</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1777.3</v>
+        <v>1716.4</v>
       </c>
       <c r="I2" t="n">
         <v>1744.673724282272</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>1.35</v>
+        <v>-2.12</v>
       </c>
       <c r="L2" t="n">
-        <v>2.52</v>
+        <v>2.83</v>
       </c>
       <c r="M2" t="n">
         <v>0.71</v>
       </c>
       <c r="N2" t="n">
-        <v>2.61</v>
+        <v>4.63</v>
       </c>
       <c r="O2" t="n">
         <v>1.96</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.42</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.38541666666</v>
+        <v>44593.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>1811.05</v>
+        <v>1838.95</v>
       </c>
       <c r="I3" t="n">
         <v>1823.834752541588</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.51</v>
+        <v>-7.14</v>
       </c>
       <c r="L3" t="n">
         <v>8.02</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.66</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1823.75</v>
+        <v>1761</v>
       </c>
       <c r="I4" t="n">
         <v>1763.258879052743</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.83</v>
+        <v>-4.24</v>
       </c>
       <c r="L4" t="n">
-        <v>4.08</v>
+        <v>4.92</v>
       </c>
       <c r="M4" t="n">
-        <v>1.28</v>
+        <v>2.26</v>
       </c>
       <c r="N4" t="n">
-        <v>3.32</v>
+        <v>4.13</v>
       </c>
       <c r="O4" t="n">
         <v>3.89</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.01</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44637.38541666666</v>
+        <v>44637.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>1803.65</v>
+        <v>1820.25</v>
       </c>
       <c r="I5" t="n">
         <v>1813.517110646517</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.42</v>
+        <v>-3.36</v>
       </c>
       <c r="L5" t="n">
         <v>5.47</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.6</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>1844.95</v>
+        <v>1793.35</v>
       </c>
       <c r="I6" t="n">
         <v>1822.348850025307</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K6" t="n">
-        <v>1.36</v>
+        <v>-1.48</v>
       </c>
       <c r="L6" t="n">
         <v>6.25</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.61</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44700.55208333334</v>
+        <v>44701.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1747.4</v>
+        <v>1797.45</v>
       </c>
       <c r="I7" t="n">
         <v>1781.66926087445</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>2.56</v>
+        <v>-0.23</v>
       </c>
       <c r="L7" t="n">
         <v>3.37</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>7.5</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44729.55208333334</v>
+        <v>44732.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1781</v>
+        <v>1745</v>
       </c>
       <c r="I8" t="n">
         <v>1757.959681396701</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.92</v>
+        <v>-2.92</v>
       </c>
       <c r="L8" t="n">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
         <v>1.26</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>7.69</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44743.55208333334</v>
+        <v>44746.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1835.95</v>
+        <v>1891.7</v>
       </c>
       <c r="I9" t="n">
         <v>1851.532337115599</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.21</v>
+        <v>-8.41</v>
       </c>
       <c r="L9" t="n">
-        <v>5.95</v>
+        <v>8.67</v>
       </c>
       <c r="M9" t="n">
         <v>0.77</v>
       </c>
       <c r="N9" t="n">
-        <v>2.61</v>
+        <v>4.69</v>
       </c>
       <c r="O9" t="n">
         <v>-2.17</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>6.93</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44775.55208333334</v>
+        <v>44776.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2083.2</v>
+        <v>1989.65</v>
       </c>
       <c r="I10" t="n">
         <v>2015.293982054639</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K10" t="n">
-        <v>10.12</v>
+        <v>5.18</v>
       </c>
       <c r="L10" t="n">
         <v>2.89</v>
       </c>
       <c r="M10" t="n">
-        <v>0.66</v>
+        <v>2.36</v>
       </c>
       <c r="N10" t="n">
-        <v>1.73</v>
+        <v>4.45</v>
       </c>
       <c r="O10" t="n">
         <v>4.69</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>7.32</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44778.55208333334</v>
+        <v>44781.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2047.05</v>
+        <v>2139.15</v>
       </c>
       <c r="I11" t="n">
         <v>2108.587507479195</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.88</v>
+        <v>-7.51</v>
       </c>
       <c r="L11" t="n">
-        <v>4.07</v>
+        <v>7.59</v>
       </c>
       <c r="M11" t="n">
         <v>1.22</v>
       </c>
       <c r="N11" t="n">
-        <v>1.42</v>
+        <v>4.89</v>
       </c>
       <c r="O11" t="n">
         <v>-4.45</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.42</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44823.38541666666</v>
+        <v>44823.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>2258.45</v>
+        <v>2245.05</v>
       </c>
       <c r="I12" t="n">
         <v>2254.410736932969</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K12" t="n">
-        <v>5.58</v>
+        <v>4.95</v>
       </c>
       <c r="L12" t="n">
         <v>4.37</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.74</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44852.55208333334</v>
+        <v>44853.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>2146.8</v>
+        <v>2198.15</v>
       </c>
       <c r="I13" t="n">
         <v>2176.98195164489</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>4.38</v>
+        <v>2.09</v>
       </c>
       <c r="L13" t="n">
         <v>2.42</v>
@@ -1182,7 +1337,7 @@
         <v>1.88</v>
       </c>
       <c r="N13" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
         <v>-0.6</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.93</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44879.55208333334</v>
+        <v>44880.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>2213.35</v>
+        <v>2171.5</v>
       </c>
       <c r="I14" t="n">
         <v>2171.661504762687</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.21</v>
       </c>
       <c r="L14" t="n">
         <v>2.89</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>5.64</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44901.55208333334</v>
+        <v>44902.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>2101.05</v>
+        <v>2221.4</v>
       </c>
       <c r="I15" t="n">
         <v>2182.897776780135</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K15" t="n">
-        <v>3.24</v>
+        <v>-2.3</v>
       </c>
       <c r="L15" t="n">
-        <v>2.37</v>
+        <v>3.42</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>2.32</v>
       </c>
       <c r="N15" t="n">
-        <v>1.88</v>
+        <v>5.41</v>
       </c>
       <c r="O15" t="n">
         <v>-1.91</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.16</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>2218</v>
+        <v>2193.9</v>
       </c>
       <c r="I16" t="n">
         <v>2205.494988414002</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.15</v>
+        <v>-1.24</v>
       </c>
       <c r="L16" t="n">
         <v>3.22</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>5.64</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44936.55208333334</v>
+        <v>44937.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>2189.4</v>
+        <v>2235.45</v>
       </c>
       <c r="I17" t="n">
         <v>2224.226869748155</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>0.21</v>
+        <v>-1.89</v>
       </c>
       <c r="L17" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
         <v>0.93</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.57</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2274.75</v>
+        <v>2228.1</v>
       </c>
       <c r="I18" t="n">
         <v>2231.137669622502</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K18" t="n">
-        <v>1.76</v>
+        <v>-0.33</v>
       </c>
       <c r="L18" t="n">
         <v>2.72</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.51</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44963.38541666666</v>
+        <v>44963.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>2322.6</v>
+        <v>2346.2</v>
       </c>
       <c r="I19" t="n">
         <v>2341.032285847059</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.24</v>
+        <v>-5.3</v>
       </c>
       <c r="L19" t="n">
-        <v>5.24</v>
+        <v>5.53</v>
       </c>
       <c r="M19" t="n">
         <v>0.82</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.69</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45034.55208333334</v>
+        <v>45035.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>2520.8</v>
+        <v>2493.7</v>
       </c>
       <c r="I20" t="n">
         <v>2497.963204190233</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>71</v>
+        <v>71.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>7.44</v>
+        <v>6.29</v>
       </c>
       <c r="L20" t="n">
         <v>1.16</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>4.26</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45041.55208333334</v>
+        <v>45042.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>2536.85</v>
+        <v>2594.85</v>
       </c>
       <c r="I21" t="n">
         <v>2551.136082057607</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.73</v>
+        <v>-4.06</v>
       </c>
       <c r="L21" t="n">
-        <v>2.56</v>
+        <v>4.24</v>
       </c>
       <c r="M21" t="n">
         <v>0.76</v>
       </c>
       <c r="N21" t="n">
-        <v>1.62</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
         <v>-1.36</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.63</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45065.38541666666</v>
+        <v>45065.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>2941.9</v>
+        <v>2766.55</v>
       </c>
       <c r="I22" t="n">
         <v>2833.461999857414</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>13.37</v>
+        <v>6.62</v>
       </c>
       <c r="L22" t="n">
         <v>2.09</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45084.38541666666</v>
+        <v>45084.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>2771.9</v>
+        <v>2788.05</v>
       </c>
       <c r="I23" t="n">
         <v>2783.301160834949</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.19</v>
+        <v>-0.78</v>
       </c>
       <c r="L23" t="n">
         <v>6.77</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.48</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45098.55208333334</v>
+        <v>45099.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>2894.85</v>
+        <v>2823.25</v>
       </c>
       <c r="I24" t="n">
         <v>2830.041911156192</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>3.83</v>
+        <v>1.26</v>
       </c>
       <c r="L24" t="n">
         <v>1.3</v>
@@ -1809,7 +2096,7 @@
         <v>0.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.86</v>
+        <v>2.82</v>
       </c>
       <c r="O24" t="n">
         <v>1.92</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>5.37</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45118.55208333334</v>
+        <v>45119.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>2872.85</v>
+        <v>2929.7</v>
       </c>
       <c r="I25" t="n">
         <v>2887.878125219594</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.76</v>
+        <v>-3.77</v>
       </c>
       <c r="L25" t="n">
-        <v>2.81</v>
+        <v>4.59</v>
       </c>
       <c r="M25" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="N25" t="n">
         <v>3.46</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>4.86</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45126.55208333334</v>
+        <v>45127.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>2824.75</v>
+        <v>2760.55</v>
       </c>
       <c r="I26" t="n">
         <v>2792.967679543424</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.58</v>
+        <v>-5.77</v>
       </c>
       <c r="L26" t="n">
-        <v>4.31</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>0.64</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>5.66</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45135.38541666666</v>
+        <v>45135.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>2890.4</v>
+        <v>2933.05</v>
       </c>
       <c r="I27" t="n">
         <v>2896.097176223891</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.7</v>
+        <v>-6.25</v>
       </c>
       <c r="L27" t="n">
-        <v>5.09</v>
+        <v>6.64</v>
       </c>
       <c r="M27" t="n">
         <v>0.37</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>4.93</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45140.55208333334</v>
+        <v>45141.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>2909.9</v>
+        <v>2858.75</v>
       </c>
       <c r="I28" t="n">
         <v>2875.198248852009</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.79</v>
+        <v>-2.53</v>
       </c>
       <c r="L28" t="n">
-        <v>1.63</v>
+        <v>2.74</v>
       </c>
       <c r="M28" t="n">
         <v>0.21</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.35</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45161.55208333334</v>
+        <v>45162.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>2830.95</v>
+        <v>2912</v>
       </c>
       <c r="I29" t="n">
         <v>2862.932969268024</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K29" t="n">
-        <v>0.97</v>
+        <v>-1.86</v>
       </c>
       <c r="L29" t="n">
         <v>3.07</v>
@@ -2094,7 +2441,7 @@
         <v>0.93</v>
       </c>
       <c r="N29" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O29" t="n">
         <v>-0.52</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.2</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45182.38541666666</v>
+        <v>45182.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>2926.4</v>
+        <v>2912.35</v>
       </c>
       <c r="I30" t="n">
         <v>2915.983201668107</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>0.49</v>
+        <v>0.01</v>
       </c>
       <c r="L30" t="n">
         <v>2.37</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>4.49</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>2603.75</v>
+        <v>2664.95</v>
       </c>
       <c r="I31" t="n">
         <v>2649.816906230101</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>61</v>
+        <v>62.83333333333334</v>
       </c>
       <c r="K31" t="n">
-        <v>10.6</v>
+        <v>8.49</v>
       </c>
       <c r="L31" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>0.92</v>
+        <v>1.38</v>
       </c>
       <c r="N31" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="O31" t="n">
         <v>-0.7</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.47</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>3067.85</v>
+        <v>2958.35</v>
       </c>
       <c r="I32" t="n">
         <v>2995.140701221295</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>15.12</v>
+        <v>11.01</v>
       </c>
       <c r="L32" t="n">
         <v>2.44</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45299.55208333334</v>
+        <v>45300.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>3062.45</v>
+        <v>3192.4</v>
       </c>
       <c r="I33" t="n">
         <v>3175.079479835837</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.52</v>
+        <v>-7.91</v>
       </c>
       <c r="L33" t="n">
-        <v>6.28</v>
+        <v>8.41</v>
       </c>
       <c r="M33" t="n">
         <v>2.97</v>
       </c>
       <c r="N33" t="n">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="O33" t="n">
         <v>-3.34</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.67</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45322.55208333334</v>
+        <v>45323.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>3155.4</v>
+        <v>3115.1</v>
       </c>
       <c r="I34" t="n">
         <v>3116.822877436481</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.16</v>
+        <v>-2.42</v>
       </c>
       <c r="L34" t="n">
         <v>5.38</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.69</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45336.38541666666</v>
+        <v>45336.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>3325.75</v>
+        <v>3350.35</v>
       </c>
       <c r="I35" t="n">
         <v>3341.554840352532</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.76</v>
+        <v>-7.55</v>
       </c>
       <c r="L35" t="n">
         <v>10.04</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.44</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>5515.45</v>
+        <v>4909</v>
       </c>
       <c r="I36" t="n">
         <v>5273.124791930893</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>110</v>
+        <v>110.8333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>64.62</v>
+        <v>46.52</v>
       </c>
       <c r="L36" t="n">
         <v>1.71</v>
@@ -2493,7 +2924,7 @@
         <v>1.21</v>
       </c>
       <c r="N36" t="n">
-        <v>3.78</v>
+        <v>11.22</v>
       </c>
       <c r="O36" t="n">
         <v>1.95</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>14.69</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45455.55208333334</v>
+        <v>45456.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>5370.75</v>
+        <v>5600.2</v>
       </c>
       <c r="I37" t="n">
         <v>5543.066363930013</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.41</v>
+        <v>-14.08</v>
       </c>
       <c r="L37" t="n">
-        <v>13.6</v>
+        <v>14.59</v>
       </c>
       <c r="M37" t="n">
         <v>2.99</v>
       </c>
       <c r="N37" t="n">
-        <v>4.4</v>
+        <v>5.18</v>
       </c>
       <c r="O37" t="n">
         <v>-11.22</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>10.03</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45489.55208333334</v>
+        <v>45491.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>5682.9</v>
+        <v>5411.7</v>
       </c>
       <c r="I38" t="n">
         <v>5682.359471830198</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K38" t="n">
-        <v>1.48</v>
+        <v>-3.37</v>
       </c>
       <c r="L38" t="n">
-        <v>3.52</v>
+        <v>4.03</v>
       </c>
       <c r="M38" t="n">
         <v>0.19</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>4.44</v>
       </c>
       <c r="O38" t="n">
         <v>5.18</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.06</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45518.55208333334</v>
+        <v>45520.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>5363.05</v>
+        <v>5517.2</v>
       </c>
       <c r="I39" t="n">
         <v>5408.292190430803</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K39" t="n">
-        <v>0.9</v>
+        <v>-1.95</v>
       </c>
       <c r="L39" t="n">
         <v>5.27</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.48</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45537.38541666666</v>
+        <v>45537.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>5180.75</v>
+        <v>5165</v>
       </c>
       <c r="I40" t="n">
         <v>5173.949662008139</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.1</v>
+        <v>-6.38</v>
       </c>
       <c r="L40" t="n">
         <v>6.63</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>3.87</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45554.55208333334</v>
+        <v>45555.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>5127.35</v>
+        <v>5185.75</v>
       </c>
       <c r="I41" t="n">
         <v>5182.736959164765</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>0.73</v>
+        <v>-0.4</v>
       </c>
       <c r="L41" t="n">
         <v>0.9399999999999999</v>
@@ -2778,7 +3269,7 @@
         <v>0.57</v>
       </c>
       <c r="N41" t="n">
-        <v>0.89</v>
+        <v>1.92</v>
       </c>
       <c r="O41" t="n">
         <v>-1.9</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>4.89</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>5506.3</v>
+        <v>5395.3</v>
       </c>
       <c r="I42" t="n">
         <v>5411.241086347711</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>6.18</v>
+        <v>4.04</v>
       </c>
       <c r="L42" t="n">
         <v>1.39</v>
@@ -2835,7 +3338,7 @@
         <v>0.5</v>
       </c>
       <c r="N42" t="n">
-        <v>1.86</v>
+        <v>3.17</v>
       </c>
       <c r="O42" t="n">
         <v>1.92</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>7.71</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45573.55208333334</v>
+        <v>45574.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>5606.1</v>
+        <v>5845.35</v>
       </c>
       <c r="I43" t="n">
         <v>5676.262064905287</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.91</v>
+        <v>-8.34</v>
       </c>
       <c r="L43" t="n">
-        <v>4.49</v>
+        <v>9.33</v>
       </c>
       <c r="M43" t="n">
         <v>1.08</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45583.55208333334</v>
+        <v>45586.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>5938.25</v>
+        <v>5736.15</v>
       </c>
       <c r="I44" t="n">
         <v>5753.757866286033</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K44" t="n">
-        <v>1.59</v>
+        <v>-1.87</v>
       </c>
       <c r="L44" t="n">
         <v>4.02</v>
@@ -2949,7 +3476,7 @@
         <v>0.06</v>
       </c>
       <c r="N44" t="n">
-        <v>3.2</v>
+        <v>3.93</v>
       </c>
       <c r="O44" t="n">
         <v>4.66</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>5218.35</v>
+        <v>5550.75</v>
       </c>
       <c r="I45" t="n">
         <v>5366.319172432113</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K45" t="n">
-        <v>9.029999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="L45" t="n">
         <v>4.56</v>
       </c>
       <c r="M45" t="n">
-        <v>1.26</v>
+        <v>1.93</v>
       </c>
       <c r="N45" t="n">
-        <v>2.65</v>
+        <v>7.23</v>
       </c>
       <c r="O45" t="n">
         <v>-3.93</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>9.02</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>5851.55</v>
+        <v>5813.75</v>
       </c>
       <c r="I46" t="n">
         <v>5833.084768867713</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>5.42</v>
+        <v>4.74</v>
       </c>
       <c r="L46" t="n">
         <v>4.32</v>
       </c>
       <c r="M46" t="n">
-        <v>0.09</v>
+        <v>1.71</v>
       </c>
       <c r="N46" t="n">
         <v>1.79</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>4.19</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>3744.25</v>
+        <v>3889</v>
       </c>
       <c r="I47" t="n">
         <v>3768.942406915491</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>75.16666666666667</v>
+        <v>76</v>
       </c>
       <c r="K47" t="n">
-        <v>35.6</v>
+        <v>33.11</v>
       </c>
       <c r="L47" t="n">
         <v>1.07</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>3997.15</v>
+        <v>3775.65</v>
       </c>
       <c r="I48" t="n">
         <v>3842.534026144695</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K48" t="n">
-        <v>2.78</v>
+        <v>-2.91</v>
       </c>
       <c r="L48" t="n">
         <v>5.77</v>
@@ -3177,7 +3752,7 @@
         <v>1.17</v>
       </c>
       <c r="N48" t="n">
-        <v>2.83</v>
+        <v>6.52</v>
       </c>
       <c r="O48" t="n">
         <v>3.56</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>11.37</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45792.55208333334</v>
+        <v>45793.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>3005</v>
+        <v>3071.8</v>
       </c>
       <c r="I49" t="n">
         <v>3028.244794785448</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K49" t="n">
-        <v>20.41</v>
+        <v>18.64</v>
       </c>
       <c r="L49" t="n">
         <v>6.68</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.67</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45827.55208333334</v>
+        <v>45828.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>3277</v>
+        <v>3208.8</v>
       </c>
       <c r="I50" t="n">
         <v>3242.452156329466</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K50" t="n">
-        <v>6.68</v>
+        <v>4.46</v>
       </c>
       <c r="L50" t="n">
         <v>2.47</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>6.97</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45838.55208333334</v>
+        <v>45839.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>3260</v>
+        <v>3328.9</v>
       </c>
       <c r="I51" t="n">
         <v>3289.486749731229</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.6</v>
+        <v>-3.74</v>
       </c>
       <c r="L51" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="M51" t="n">
         <v>1.02</v>
       </c>
       <c r="N51" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O51" t="n">
         <v>-2.08</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>6.68</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>3189</v>
+        <v>3117.5</v>
       </c>
       <c r="I52" t="n">
         <v>3139.965399344072</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.2</v>
+        <v>-6.35</v>
       </c>
       <c r="L52" t="n">
-        <v>4.86</v>
+        <v>6.67</v>
       </c>
       <c r="M52" t="n">
-        <v>0.15</v>
+        <v>0.34</v>
       </c>
       <c r="N52" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="O52" t="n">
         <v>2.2</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.3</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45874.55208333334</v>
+        <v>45875.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>3084.9</v>
+        <v>3100.5</v>
       </c>
       <c r="I53" t="n">
         <v>3099.063804191167</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K53" t="n">
-        <v>1.05</v>
+        <v>0.55</v>
       </c>
       <c r="L53" t="n">
         <v>2.34</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.08</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45895.38541666666</v>
+        <v>45895.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>3080</v>
+        <v>3050</v>
       </c>
       <c r="I54" t="n">
         <v>3069.726691659033</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.66</v>
+        <v>-1.63</v>
       </c>
       <c r="L54" t="n">
         <v>5.66</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.17</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45902.55208333334</v>
+        <v>45903.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>3192.1</v>
+        <v>3214</v>
       </c>
       <c r="I55" t="n">
         <v>3209.769041997229</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.66</v>
+        <v>-5.38</v>
       </c>
       <c r="L55" t="n">
-        <v>4.85</v>
+        <v>5.73</v>
       </c>
       <c r="M55" t="n">
         <v>0.35</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.07</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45924.55208333334</v>
+        <v>45925.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>3205</v>
+        <v>3177</v>
       </c>
       <c r="I56" t="n">
         <v>3203.55930921265</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.28</v>
+        <v>-1.15</v>
       </c>
       <c r="L56" t="n">
         <v>4.01</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>4.5</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>3168</v>
+        <v>3239.4</v>
       </c>
       <c r="I57" t="n">
         <v>3215.056418644735</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K57" t="n">
-        <v>0.28</v>
+        <v>-1.96</v>
       </c>
       <c r="L57" t="n">
-        <v>1.42</v>
+        <v>2.34</v>
       </c>
       <c r="M57" t="n">
         <v>0.45</v>
       </c>
       <c r="N57" t="n">
-        <v>1.28</v>
+        <v>2.27</v>
       </c>
       <c r="O57" t="n">
         <v>-1.37</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.27</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45940.55208333334</v>
+        <v>45943.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>3150</v>
+        <v>3065.5</v>
       </c>
       <c r="I58" t="n">
         <v>3121.671845628091</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.76</v>
+        <v>-5.37</v>
       </c>
       <c r="L58" t="n">
-        <v>3.07</v>
+        <v>6.69</v>
       </c>
       <c r="M58" t="n">
         <v>0.16</v>
       </c>
       <c r="N58" t="n">
-        <v>1.14</v>
+        <v>2.22</v>
       </c>
       <c r="O58" t="n">
         <v>2.27</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.59</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45975.55208333334</v>
+        <v>45978.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>3093.4</v>
+        <v>3218.2</v>
       </c>
       <c r="I59" t="n">
         <v>3139.151669368007</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.91</v>
+        <v>-4.98</v>
       </c>
       <c r="L59" t="n">
-        <v>3.65</v>
+        <v>5.33</v>
       </c>
       <c r="M59" t="n">
         <v>0.96</v>
       </c>
       <c r="N59" t="n">
-        <v>1.61</v>
+        <v>4.67</v>
       </c>
       <c r="O59" t="n">
         <v>-2.22</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.66</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45999.38541666666</v>
+        <v>45999.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>3238.3</v>
+        <v>3196.1</v>
       </c>
       <c r="I60" t="n">
         <v>3228.510638621027</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>0.62</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L60" t="n">
         <v>3.88</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.44</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46050.55208333334</v>
+        <v>46051.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>2978.1</v>
+        <v>3071</v>
       </c>
       <c r="I61" t="n">
         <v>3021.809424849353</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>51</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K61" t="n">
-        <v>6.82</v>
+        <v>3.91</v>
       </c>
       <c r="L61" t="n">
         <v>1.32</v>
@@ -3918,7 +4649,7 @@
         <v>0.93</v>
       </c>
       <c r="N61" t="n">
-        <v>2.69</v>
+        <v>3.96</v>
       </c>
       <c r="O61" t="n">
         <v>-3.73</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.68</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46085.38541666666</v>
+        <v>46085.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>3192</v>
+        <v>3150</v>
       </c>
       <c r="I62" t="n">
         <v>3191.305668214874</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>3.94</v>
+        <v>2.57</v>
       </c>
       <c r="L62" t="n">
         <v>5.85</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46120.38541666666</v>
+        <v>46120.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>3186</v>
+        <v>3233.4</v>
       </c>
       <c r="I63" t="n">
         <v>3189.856398536011</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>34.83333333333334</v>
+        <v>35</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.14</v>
+        <v>-2.65</v>
       </c>
       <c r="L63" t="n">
         <v>6.73</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>8</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46150.55208333334</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>3838</v>
+        <v>3619.6</v>
       </c>
       <c r="I64" t="n">
         <v>3679.355588161802</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K64" t="n">
-        <v>18.7</v>
+        <v>11.94</v>
       </c>
       <c r="L64" t="n">
         <v>1.68</v>
       </c>
       <c r="M64" t="n">
-        <v>1.76</v>
+        <v>3.07</v>
       </c>
       <c r="N64" t="n">
-        <v>1.44</v>
+        <v>6.48</v>
       </c>
       <c r="O64" t="n">
         <v>5.11</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>8</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46163.55208333334</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>3723</v>
+        <v>3830.6</v>
       </c>
       <c r="I65" t="n">
         <v>3788.88985568158</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.86</v>
+        <v>-5.83</v>
       </c>
       <c r="L65" t="n">
-        <v>4.43</v>
+        <v>5.87</v>
       </c>
       <c r="M65" t="n">
         <v>0.96</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.42</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46183.38541666666</v>
+        <v>46183.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>3613.7</v>
+        <v>3560.1</v>
       </c>
       <c r="I66" t="n">
         <v>3565.605271305623</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-5.66</v>
+        <v>-7.06</v>
       </c>
       <c r="L66" t="n">
         <v>7.5</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>6.97</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46191.38541666666</v>
+        <v>46191.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>3732</v>
+        <v>3746.1</v>
       </c>
       <c r="I67" t="n">
         <v>3737.961555202589</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.83</v>
+        <v>-5.22</v>
       </c>
       <c r="L67" t="n">
-        <v>5.12</v>
+        <v>5.47</v>
       </c>
       <c r="M67" t="n">
         <v>1.85</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>5.47</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46197.38541666666</v>
+        <v>46197.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>3607</v>
+        <v>3558</v>
       </c>
       <c r="I68" t="n">
         <v>3574.014135125798</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.71</v>
+        <v>-5.02</v>
       </c>
       <c r="L68" t="n">
-        <v>4.38</v>
+        <v>5.23</v>
       </c>
       <c r="M68" t="n">
         <v>0.05</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>6.63</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46218.55208333334</v>
+        <v>46219.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>3577</v>
+        <v>3665.8</v>
       </c>
       <c r="I69" t="n">
         <v>3636.96369116023</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.53</v>
+        <v>-3.03</v>
       </c>
       <c r="L69" t="n">
-        <v>3.1</v>
+        <v>8.35</v>
       </c>
       <c r="M69" t="n">
         <v>0.65</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.57</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46276.55208333334</v>
+        <v>46280.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>3931</v>
+        <v>3831.3</v>
       </c>
       <c r="I70" t="n">
         <v>3910.557681655285</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K70" t="n">
-        <v>7.23</v>
+        <v>4.51</v>
       </c>
       <c r="L70" t="n">
         <v>2.92</v>
@@ -4431,7 +5270,7 @@
         <v>1.19</v>
       </c>
       <c r="N70" t="n">
-        <v>1.88</v>
+        <v>4.02</v>
       </c>
       <c r="O70" t="n">
         <v>2.04</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>58</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7452,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.7</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7462,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7472,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110</v>
+        <v>110.8</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7482,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7492,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7502,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41.3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -6653,7 +7512,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -6663,7 +7522,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -6673,7 +7532,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76.8</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="14">
@@ -6683,7 +7542,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.57</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.27</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7562,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.82</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7572,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>64.62</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7582,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.2</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7592,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.98</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7602,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.65</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7612,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.6</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7622,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -6783,7 +7642,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="25">
@@ -6803,7 +7662,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.8</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7672,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.22</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7682,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
